--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_1.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_1.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.008537925062941961</v>
+        <v>0.0009287793992768571</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008415597809022419</v>
+        <v>0.008408531073609142</v>
       </c>
       <c r="C2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>4801066</v>
+        <v>5027671</v>
       </c>
       <c r="L2" t="n">
-        <v>2965847</v>
+        <v>3251527</v>
       </c>
       <c r="M2" t="n">
-        <v>781552</v>
+        <v>895851</v>
       </c>
       <c r="N2" t="n">
-        <v>45366</v>
+        <v>63376</v>
       </c>
       <c r="O2" t="n">
-        <v>458812</v>
+        <v>508063</v>
       </c>
       <c r="P2" t="n">
-        <v>179091</v>
+        <v>191601</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999990463256836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9565759301185608</v>
+        <v>0.999267578125</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9012269973754883</v>
+        <v>0.9843665361404419</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8549026250839233</v>
+        <v>0.9783899188041687</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7105869054794312</v>
+        <v>0.9912102222442627</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8993580341339111</v>
+        <v>0.9952086806297302</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9327267408370972</v>
+        <v>0.9978802800178528</v>
       </c>
       <c r="X2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>4808782</v>
+        <v>4825783</v>
       </c>
       <c r="AG2" t="n">
-        <v>2955373</v>
+        <v>2962430</v>
       </c>
       <c r="AH2" t="n">
-        <v>798205</v>
+        <v>798977</v>
       </c>
       <c r="AI2" t="n">
-        <v>58883</v>
+        <v>58950</v>
       </c>
       <c r="AJ2" t="n">
-        <v>458685</v>
+        <v>458776</v>
       </c>
       <c r="AK2" t="n">
         <v>180009</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566851854324341</v>
+        <v>0.9567543864250183</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112403392791748</v>
+        <v>0.9111810326576233</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8584150671958923</v>
+        <v>0.8583831191062927</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6629027724266052</v>
+        <v>0.6629480123519897</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9021613597869873</v>
+        <v>0.9021487236022949</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,88 +786,88 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00195713680898159</v>
+        <v>0.0001995517389827983</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002018522500489981</v>
+        <v>0.002016202349440813</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4801066</v>
+        <v>5027671</v>
       </c>
       <c r="E3" t="n">
-        <v>212950</v>
+        <v>11205</v>
       </c>
       <c r="F3" t="n">
-        <v>6383</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>647</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9990117</v>
+        <v>10016616</v>
       </c>
       <c r="K3" t="n">
-        <v>11047319</v>
+        <v>11287017</v>
       </c>
       <c r="L3" t="n">
-        <v>12713585</v>
+        <v>13022643</v>
       </c>
       <c r="M3" t="n">
-        <v>15223362</v>
+        <v>15378459</v>
       </c>
       <c r="N3" t="n">
-        <v>16179024</v>
+        <v>16240033</v>
       </c>
       <c r="O3" t="n">
-        <v>15726384</v>
+        <v>15818369</v>
       </c>
       <c r="P3" t="n">
-        <v>16080220</v>
+        <v>16135930</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.956171452999115</v>
+        <v>0.9977719187736511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.913196861743927</v>
+        <v>0.9988357424736023</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8400261998176575</v>
+        <v>0.9618802070617676</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5103094577789307</v>
+        <v>0.7120499014854431</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9019783139228821</v>
+        <v>0.9985809326171875</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9266698956489563</v>
+        <v>0.9914003014564514</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4808782</v>
+        <v>4825783</v>
       </c>
       <c r="Z3" t="n">
-        <v>197044</v>
+        <v>197772</v>
       </c>
       <c r="AA3" t="n">
-        <v>8483</v>
+        <v>8501</v>
       </c>
       <c r="AB3" t="n">
-        <v>6751</v>
+        <v>6767</v>
       </c>
       <c r="AC3" t="n">
         <v>45</v>
@@ -876,43 +876,43 @@
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>9990123</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>11047543</v>
+        <v>11072575</v>
       </c>
       <c r="AG3" t="n">
-        <v>12750768</v>
+        <v>12785515</v>
       </c>
       <c r="AH3" t="n">
-        <v>15224356</v>
+        <v>15266430</v>
       </c>
       <c r="AI3" t="n">
-        <v>16167558</v>
+        <v>16210624</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15727983</v>
+        <v>15771054</v>
       </c>
       <c r="AK3" t="n">
-        <v>16079883</v>
+        <v>16123083</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577081799507141</v>
+        <v>0.9577060341835022</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099718928337097</v>
+        <v>0.9100281000137329</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8579251766204834</v>
+        <v>0.8578660488128662</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6623584032058716</v>
+        <v>0.6623223423957825</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901728630065918</v>
+        <v>0.9017089605331421</v>
       </c>
       <c r="AR3" t="n">
         <v>0.931419849395752</v>
@@ -920,88 +920,88 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03228661648138429</v>
+        <v>0.008134641335162099</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03185503593778934</v>
+        <v>0.03183346841779339</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>203685</v>
+        <v>3469</v>
       </c>
       <c r="E4" t="n">
-        <v>2965847</v>
+        <v>3251527</v>
       </c>
       <c r="F4" t="n">
-        <v>75739</v>
+        <v>314</v>
       </c>
       <c r="G4" t="n">
-        <v>1283</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1166</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>217946</v>
+        <v>3685</v>
       </c>
       <c r="L4" t="n">
-        <v>325052</v>
+        <v>51640</v>
       </c>
       <c r="M4" t="n">
-        <v>132648</v>
+        <v>19787</v>
       </c>
       <c r="N4" t="n">
-        <v>18477</v>
+        <v>562</v>
       </c>
       <c r="O4" t="n">
-        <v>51343</v>
+        <v>2446</v>
       </c>
       <c r="P4" t="n">
-        <v>12917</v>
+        <v>407</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999995231628418</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9563736915588379</v>
+        <v>0.9985191226005554</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9071725010871887</v>
+        <v>0.9915483593940735</v>
       </c>
       <c r="T4" t="n">
-        <v>0.847399115562439</v>
+        <v>0.9700648188591003</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5940213203430176</v>
+        <v>0.8287531733512878</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9006662964820862</v>
+        <v>0.9968919157981873</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9296884536743164</v>
+        <v>0.9946297407150269</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>203271</v>
+        <v>203648</v>
       </c>
       <c r="Z4" t="n">
-        <v>2955373</v>
+        <v>2962430</v>
       </c>
       <c r="AA4" t="n">
-        <v>82450</v>
+        <v>82563</v>
       </c>
       <c r="AB4" t="n">
-        <v>5465</v>
+        <v>5472</v>
       </c>
       <c r="AC4" t="n">
         <v>1136</v>
@@ -1013,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>217722</v>
+        <v>218127</v>
       </c>
       <c r="AG4" t="n">
-        <v>287869</v>
+        <v>288768</v>
       </c>
       <c r="AH4" t="n">
-        <v>131654</v>
+        <v>131816</v>
       </c>
       <c r="AI4" t="n">
-        <v>29943</v>
+        <v>29971</v>
       </c>
       <c r="AJ4" t="n">
-        <v>49744</v>
+        <v>49761</v>
       </c>
       <c r="AK4" t="n">
         <v>13254</v>
@@ -1034,19 +1034,19 @@
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571964144706726</v>
+        <v>0.9572299718856812</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106056094169617</v>
+        <v>0.9106041789054871</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8581700325012207</v>
+        <v>0.8581244349479675</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6626304984092712</v>
+        <v>0.6626349687576294</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9019449949264526</v>
+        <v>0.9019287824630737</v>
       </c>
       <c r="AR4" t="n">
         <v>0.931419849395752</v>
@@ -1059,82 +1059,82 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7946</v>
+        <v>115</v>
       </c>
       <c r="E5" t="n">
-        <v>102372</v>
+        <v>35209</v>
       </c>
       <c r="F5" t="n">
-        <v>781552</v>
+        <v>895851</v>
       </c>
       <c r="G5" t="n">
-        <v>8791</v>
+        <v>175</v>
       </c>
       <c r="H5" t="n">
-        <v>29165</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>220069</v>
+        <v>11227</v>
       </c>
       <c r="L5" t="n">
-        <v>281916</v>
+        <v>3790</v>
       </c>
       <c r="M5" t="n">
-        <v>148838</v>
+        <v>35503</v>
       </c>
       <c r="N5" t="n">
-        <v>43533</v>
+        <v>25629</v>
       </c>
       <c r="O5" t="n">
-        <v>49861</v>
+        <v>722</v>
       </c>
       <c r="P5" t="n">
-        <v>14172</v>
+        <v>1662</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999996423721313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9731054902076721</v>
+        <v>0.9990867972373962</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9627315998077393</v>
+        <v>0.9966055750846863</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9827165007591248</v>
+        <v>0.9966140985488892</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9961925148963928</v>
+        <v>0.998396098613739</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9937859773635864</v>
+        <v>0.9998059868812561</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9983367323875427</v>
+        <v>0.9998732805252075</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>7974</v>
+        <v>7991</v>
       </c>
       <c r="Z5" t="n">
-        <v>84616</v>
+        <v>84775</v>
       </c>
       <c r="AA5" t="n">
-        <v>798205</v>
+        <v>798977</v>
       </c>
       <c r="AB5" t="n">
-        <v>9906</v>
+        <v>9911</v>
       </c>
       <c r="AC5" t="n">
-        <v>29056</v>
+        <v>29067</v>
       </c>
       <c r="AD5" t="n">
         <v>633</v>
@@ -1143,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>212353</v>
+        <v>213115</v>
       </c>
       <c r="AG5" t="n">
-        <v>292390</v>
+        <v>292887</v>
       </c>
       <c r="AH5" t="n">
-        <v>132185</v>
+        <v>132377</v>
       </c>
       <c r="AI5" t="n">
-        <v>30016</v>
+        <v>30055</v>
       </c>
       <c r="AJ5" t="n">
-        <v>49988</v>
+        <v>50009</v>
       </c>
       <c r="AK5" t="n">
         <v>13254</v>
@@ -1164,47 +1164,47 @@
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97359299659729</v>
+        <v>0.9735913872718811</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643715620040894</v>
+        <v>0.9643803238868713</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838000535964966</v>
+        <v>0.9838212132453918</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963184595108032</v>
+        <v>0.9963241219520569</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938763380050659</v>
+        <v>0.9938902258872986</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983723759651184</v>
+        <v>0.9983766674995422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6279</v>
+        <v>101</v>
       </c>
       <c r="E6" t="n">
-        <v>8817</v>
+        <v>5222</v>
       </c>
       <c r="F6" t="n">
-        <v>20640</v>
+        <v>19436</v>
       </c>
       <c r="G6" t="n">
-        <v>45366</v>
+        <v>63376</v>
       </c>
       <c r="H6" t="n">
-        <v>7415</v>
+        <v>831</v>
       </c>
       <c r="I6" t="n">
-        <v>380</v>
+        <v>39</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>6422</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>5319</v>
+        <v>5328</v>
       </c>
       <c r="AA6" t="n">
-        <v>10837</v>
+        <v>10850</v>
       </c>
       <c r="AB6" t="n">
-        <v>58883</v>
+        <v>58950</v>
       </c>
       <c r="AC6" t="n">
-        <v>6957</v>
+        <v>6963</v>
       </c>
       <c r="AD6" t="n">
         <v>481</v>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>811</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>29553</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>7553</v>
+        <v>348</v>
       </c>
       <c r="H7" t="n">
-        <v>458812</v>
+        <v>508063</v>
       </c>
       <c r="I7" t="n">
-        <v>11921</v>
+        <v>368</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1301,16 +1301,16 @@
         <v>27</v>
       </c>
       <c r="Z7" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>29554</v>
+        <v>29572</v>
       </c>
       <c r="AB7" t="n">
         <v>7556</v>
       </c>
       <c r="AC7" t="n">
-        <v>458685</v>
+        <v>458776</v>
       </c>
       <c r="AD7" t="n">
         <v>12042</v>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>333</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>203</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>13517</v>
+        <v>1611</v>
       </c>
       <c r="I8" t="n">
-        <v>179091</v>
+        <v>191601</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
